--- a/data/trans_bre/P16A09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,69</t>
+          <t>-1,0; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,68</t>
+          <t>1,89; 5,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,58</t>
+          <t>0,94; 4,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,71</t>
+          <t>2,02; 5,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 131,69</t>
+          <t>-28,45; 123,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,24; 520,73</t>
+          <t>63,82; 490,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,12; 564,67</t>
+          <t>38,65; 570,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,92; 339,68</t>
+          <t>40,69; 320,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,9</t>
+          <t>0,32; 3,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,84</t>
+          <t>2,34; 5,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,84</t>
+          <t>1,13; 4,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,71</t>
+          <t>2,13; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 203,41</t>
+          <t>6,55; 198,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,67; 343,43</t>
+          <t>68,34; 330,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,36; 416,89</t>
+          <t>55,96; 439,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>100,15; 592,9</t>
+          <t>99,32; 601,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,87</t>
+          <t>1,55; 5,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,81</t>
+          <t>0,94; 4,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,85</t>
+          <t>0,42; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,88</t>
+          <t>-0,51; 3,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,3; 340,16</t>
+          <t>38,66; 327,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 443,68</t>
+          <t>19,51; 446,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,39; 315,95</t>
+          <t>11,96; 327,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 263,11</t>
+          <t>-19,91; 279,5</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,07</t>
+          <t>0,38; 4,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,11</t>
+          <t>2,38; 6,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,18</t>
+          <t>1,49; 4,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,55</t>
+          <t>2,79; 6,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 159,41</t>
+          <t>7,1; 164,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,04; 429,05</t>
+          <t>71,04; 406,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,19; 994,86</t>
+          <t>89,91; 916,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>106,59; 470,89</t>
+          <t>109,01; 473,38</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,08</t>
+          <t>1,18; 3,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,68</t>
+          <t>2,8; 4,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,27</t>
+          <t>1,66; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,25</t>
+          <t>2,25; 4,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,77; 123,17</t>
+          <t>34,83; 123,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>112,72; 268,35</t>
+          <t>110,35; 274,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>107,08; 320,14</t>
+          <t>93,59; 309,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>112,42; 307,66</t>
+          <t>115,25; 301,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A09-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A09-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>159,3%</t>
+          <t>166,93%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,67</t>
+          <t>-0,95; 2,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,72</t>
+          <t>1,7; 5,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,49</t>
+          <t>1,01; 4,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,61</t>
+          <t>2,26; 5,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 123,83</t>
+          <t>-25,17; 113,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,82; 490,16</t>
+          <t>56,66; 519,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,65; 570,14</t>
+          <t>45,84; 662,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,69; 320,62</t>
+          <t>59,06; 364,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>3,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>240,45%</t>
+          <t>180,71%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,91</t>
+          <t>0,14; 3,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,93</t>
+          <t>2,26; 5,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,07</t>
+          <t>0,99; 3,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,8</t>
+          <t>1,95; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 198,9</t>
+          <t>1,8; 175,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,34; 330,52</t>
+          <t>70,35; 341,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,96; 439,83</t>
+          <t>42,27; 378,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>99,32; 601,51</t>
+          <t>77,89; 378,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>158,56%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,73</t>
+          <t>1,4; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,75</t>
+          <t>0,86; 4,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,9</t>
+          <t>0,46; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,15</t>
+          <t>0,98; 3,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,66; 327,68</t>
+          <t>36,02; 353,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 446,75</t>
+          <t>25,23; 465,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 327,74</t>
+          <t>8,85; 312,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 279,5</t>
+          <t>41,87; 403,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>248,19%</t>
+          <t>243,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,19</t>
+          <t>0,48; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,03</t>
+          <t>2,5; 6,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,39</t>
+          <t>1,51; 4,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,34</t>
+          <t>3,37; 6,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 164,43</t>
+          <t>8,83; 152,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,04; 406,49</t>
+          <t>83,04; 435,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,91; 916,68</t>
+          <t>91,82; 877,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>109,01; 473,38</t>
+          <t>124,56; 442,85</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>190,69%</t>
+          <t>192,95%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,15</t>
+          <t>1,2; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,7</t>
+          <t>2,84; 4,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,23</t>
+          <t>1,73; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,19</t>
+          <t>2,81; 4,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,83; 123,14</t>
+          <t>34,95; 124,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>110,35; 274,43</t>
+          <t>112,6; 278,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,59; 309,86</t>
+          <t>106,21; 296,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>115,25; 301,29</t>
+          <t>127,79; 277,13</t>
         </is>
       </c>
     </row>
